--- a/InputData/hydgn/EHPpUC/Electrolyzer Hydrogen Production per Unit Capacity.xlsx
+++ b/InputData/hydgn/EHPpUC/Electrolyzer Hydrogen Production per Unit Capacity.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-2.0.0-us-wipF\InputData\hydgn\EHPpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-texas\InputData\hydgn\EHPpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3B8A797B2AF3831140CD665BDBE6757219A666AC" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{90F6642B-2B21-45C6-954D-C78FD0C92468}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5445"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Calculations" sheetId="3" r:id="rId2"/>
     <sheet name="EHPpUC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Source:</t>
   </si>
@@ -102,13 +95,22 @@
   </si>
   <si>
     <t>BTU H2 / MW (annual production)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The study they are citing uses 3 scenarios of Fuel Cell Electric Vehicle adoption. Then it calculates the amount of hydrogen needed to suppor those vehicles. Then it calculates the electrolyzer capacity needed to supply that hydrogen. </t>
+  </si>
+  <si>
+    <t>So, I think it's fair, using the EPS assumptions of 24/7/365 operation, that smallest electrolyzer you would need to produce 1.39e10 annual Btu would be 1 MW.</t>
+  </si>
+  <si>
+    <t>No reason to think this would be different for Texas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +130,38 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Open Sans"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -160,7 +194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -173,6 +207,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -453,16 +503,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,76 +520,82 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2018</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.1328125" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -553,8 +609,18 @@
       <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -568,8 +634,18 @@
         <f>B3/C3</f>
         <v>264.14473684210526</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -580,11 +656,16 @@
         <v>608</v>
       </c>
       <c r="E4" s="5">
-        <f t="shared" ref="E4:E5" si="0">B4/C4</f>
+        <f>B4/C4</f>
         <v>264.14473684210526</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -595,18 +676,35 @@
         <v>1140</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E5" si="0">B5/C5</f>
         <v>264.14473684210526</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>23874</v>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.4">
+      <c r="A8" s="9">
+        <v>60920</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -615,50 +713,180 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="9" spans="1:15" ht="15.4">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="12" spans="1:15">
+      <c r="A12">
         <v>2204.62</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="C12" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="C13" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <f>E3*A11*A8</f>
-        <v>13902755788.697367</v>
-      </c>
+      <c r="C14" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="6">
+        <f>E3*A12*A8</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="D16" s="14"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="4:9">
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="4:9">
+      <c r="D18" s="14"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="4:9">
+      <c r="D19" s="14"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="4:9">
+      <c r="D20" s="14"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="4:9">
+      <c r="D21" s="14"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+    </row>
+    <row r="22" spans="4:9">
+      <c r="D22" s="14"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+    </row>
+    <row r="23" spans="4:9">
+      <c r="D23" s="14"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+    </row>
+    <row r="24" spans="4:9">
+      <c r="D24" s="14"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+    </row>
+    <row r="25" spans="4:9">
+      <c r="D25" s="14"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+    </row>
+    <row r="26" spans="4:9">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+    </row>
+    <row r="27" spans="4:9">
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="4:9">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C8" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35">
       <c r="B1">
         <v>2017</v>
       </c>
@@ -762,145 +990,145 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="C2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="D2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="E2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="F2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="G2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="H2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="I2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="J2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="K2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="L2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="M2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="N2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="O2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="P2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="Q2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="R2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="S2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="T2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="U2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="V2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="W2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="X2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="Y2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="Z2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AA2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AB2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AC2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AD2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AE2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AF2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AG2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AH2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
       <c r="AI2" s="6">
-        <f>Calculations!$A$14</f>
-        <v>13902755788.697367</v>
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
       </c>
     </row>
   </sheetData>
@@ -909,49 +1137,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -959,24 +1170,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -995,70 +1267,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1160,40 +1385,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60D0CC07-0C0E-4DDD-B426-DF968E349D8F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6C25864-208F-4E73-90A1-6A1214C2724D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00A92544-FE8D-4F6A-A7E9-0A441FA939AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BCA2072-481B-42F2-B79D-4B88EE97A70E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA50AD82-098F-474E-A91F-829DE74FC4B9}"/>
 </file>